--- a/results/Int All Data -0.0/Linea_fi_all.xlsx
+++ b/results/Int All Data -0.0/Linea_fi_all.xlsx
@@ -2576,12 +2576,12 @@
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
+          <t>-0.00038207711010764813 +/- 0.00018704983699666922</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
           <t>-0.0003473428273705892 +/- 0.0001553364346995224</t>
-        </is>
-      </c>
-      <c r="DR3" t="inlineStr">
-        <is>
-          <t>-0.00038207711010764813 +/- 0.00018704983699666922</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.005986159169550154 +/- 0.0013583243201654549</t>
+          <t>0.006020761245674721 +/- 0.0013239533889072169</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.0100692041522491 +/- 0.0017053593813635291</t>
+          <t>0.010103806228373669 +/- 0.0017217792809169023</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>0.004719562243502085 +/- 0.001424942999726377</t>
+          <t>0.00475376196990428 +/- 0.0014384227664030844</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
@@ -4341,74 +4341,74 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>0.018458961474036827 +/- 0.0016913776296635628</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.0005695142378559393 +/- 0.0013404521958956602</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-0.0022445561139028737 +/- 0.002166186018134319</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-0.002378559463986618 +/- 0.001053546746634247</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.0017755443886096956 +/- 0.0006365159128977972</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.00559463986599662 +/- 0.0007347307269501025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.0008040201005025338 +/- 0.0005645661489565548</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.0005695142378559614 +/- 0.000368509212730328</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.00010050251256281673 +/- 0.0001535201237841193</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>-0.0070686767169179324 +/- 0.0012575091711305346</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-0.04033500837520939 +/- 0.0024627103449901848</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>-0.004723618090452264 +/- 0.0021939851698536436</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-0.0055611390284757145 +/- 0.0019139506676161622</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>0.01842546063651589 +/- 0.0016817286965509059</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.0005695142378559393 +/- 0.0013404521958956602</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-0.0022445561139028737 +/- 0.002166186018134319</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-0.002378559463986618 +/- 0.001053546746634247</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.0017755443886096956 +/- 0.0006365159128977972</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.00559463986599662 +/- 0.0007347307269501025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.0008040201005025338 +/- 0.0005645661489565548</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.0005695142378559614 +/- 0.000368509212730328</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.00010050251256281673 +/- 0.0001535201237841193</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>-0.0070686767169179324 +/- 0.0012575091711305346</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-0.04033500837520939 +/- 0.0024627103449901848</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>-0.004723618090452264 +/- 0.0021939851698536436</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-0.0055611390284757145 +/- 0.0019139506676161622</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.018458961474036827 +/- 0.0016913776296635628</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>0.0018090452261306234 +/- 0.0008368506530516929</t>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>-0.05172529313232831 +/- 0.0037008950029189898</t>
+          <t>-0.05169179229480737 +/- 0.0036791485493578987</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>6.451612903229931e-05 +/- 0.0006888437581955722</t>
+          <t>9.67741935484212e-05 +/- 0.0006774193548387159</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.0055845122859270015 +/- 0.0009989879274012237</t>
+          <t>0.0055845122859270015 +/- 0.001116902457185387</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0.011653015636634368 +/- 0.003404262990497741</t>
+          <t>0.011690245718540548 +/- 0.0034008003713087934</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.003834698436336581 +/- 0.002283208951073991</t>
+          <t>-0.0038719285182427622 +/- 0.002284119382007126</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>-0.03008190618019364 +/- 0.0035702076231531993</t>
+          <t>-0.03004467609828746 +/- 0.003559515153428971</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>0.003410689170182879 +/- 0.0014501821819480508</t>
+          <t>0.003375527426160374 +/- 0.0014343233512215982</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-0.0004922644163150358 +/- 0.0006890266505719043</t>
+          <t>-0.0005274261603375408 +/- 0.0007582228780888695</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>0.04690576652601972 +/- 0.0036071219699668525</t>
+          <t>0.04687060478199721 +/- 0.003585980768543655</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>0.007137834036568225 +/- 0.0010786119303922569</t>
+          <t>0.007102672292545719 +/- 0.0010406925869865435</t>
         </is>
       </c>
       <c r="DC9" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>0.01258790436005629 +/- 0.00186589299035465</t>
+          <t>0.012623066104078784 +/- 0.0018767941132324135</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.038670694864048324 +/- 0.0027996857283642913</t>
+          <t>0.03870426317556226 +/- 0.002784551635769117</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.01399798590130914 +/- 0.0012742700836591036</t>
+          <t>0.013964417589795209 +/- 0.0012306346277155674</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="DN11" t="inlineStr">
         <is>
-          <t>-0.0003917727717923758 +/- 0.0010609256813105957</t>
+          <t>-0.00042442050277506914 +/- 0.0010431959065406685</t>
         </is>
       </c>
       <c r="DO11" t="inlineStr">
